--- a/data/trans_dic/P33_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,25; 85,58</t>
+          <t>78,6; 85,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,41; 79,83</t>
+          <t>71,81; 80,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,88; 82,13</t>
+          <t>74,02; 82,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72,85; 80,8</t>
+          <t>72,38; 80,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,67; 85,58</t>
+          <t>76,94; 86,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,33; 83,98</t>
+          <t>75,14; 84,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,05; 83,66</t>
+          <t>74,86; 84,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,63; 75,89</t>
+          <t>68,53; 75,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,04; 84,86</t>
+          <t>78,99; 84,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,41; 80,76</t>
+          <t>74,19; 80,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,94; 82,15</t>
+          <t>76,3; 82,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,15; 77,57</t>
+          <t>72,12; 77,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,17; 90,16</t>
+          <t>82,01; 89,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,46; 78,66</t>
+          <t>69,53; 78,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 78,19</t>
+          <t>69,2; 78,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,01; 80,42</t>
+          <t>72,11; 80,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,89; 85,81</t>
+          <t>77,61; 85,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,44; 76,86</t>
+          <t>66,86; 76,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,3; 83,83</t>
+          <t>75,16; 83,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,64; 76,21</t>
+          <t>67,8; 75,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,2; 86,89</t>
+          <t>81,37; 86,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,81; 76,5</t>
+          <t>69,68; 76,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,48; 80,04</t>
+          <t>73,48; 79,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,93; 77,66</t>
+          <t>72,21; 77,55</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,93; 83,99</t>
+          <t>77,23; 84,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,0; 76,74</t>
+          <t>69,07; 76,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,06; 78,7</t>
+          <t>70,99; 78,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66,03; 92,05</t>
+          <t>65,84; 92,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,59; 80,7</t>
+          <t>66,74; 80,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,16; 76,58</t>
+          <t>64,65; 76,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,39; 82,57</t>
+          <t>67,34; 82,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,14; 75,22</t>
+          <t>64,41; 75,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75,95; 82,17</t>
+          <t>75,78; 82,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,37; 75,57</t>
+          <t>68,95; 75,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,05; 78,51</t>
+          <t>71,52; 78,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66,7; 90,23</t>
+          <t>67,38; 90,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,19; 79,97</t>
+          <t>75,6; 80,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,04; 75,34</t>
+          <t>70,03; 75,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,03; 78,14</t>
+          <t>72,6; 78,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,75; 76,12</t>
+          <t>69,84; 75,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,69; 81,62</t>
+          <t>75,57; 81,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,37; 74,14</t>
+          <t>67,49; 74,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,62; 73,89</t>
+          <t>67,58; 74,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,53; 66,6</t>
+          <t>25,52; 67,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,38; 80,15</t>
+          <t>76,41; 80,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,98; 74,08</t>
+          <t>69,72; 73,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,5; 75,62</t>
+          <t>71,66; 75,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,16; 70,85</t>
+          <t>42,49; 70,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,77; 83,6</t>
+          <t>74,67; 83,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,79; 75,52</t>
+          <t>67,51; 75,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,04; 80,99</t>
+          <t>74,04; 80,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,39; 77,95</t>
+          <t>69,93; 78,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,6; 78,9</t>
+          <t>71,59; 79,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,66; 65,84</t>
+          <t>58,49; 65,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,37; 72,27</t>
+          <t>65,22; 72,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,63; 77,86</t>
+          <t>64,92; 77,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,78; 79,47</t>
+          <t>73,59; 79,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,94; 68,62</t>
+          <t>62,95; 68,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,29; 75,25</t>
+          <t>70,46; 75,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,71; 75,9</t>
+          <t>67,86; 76,04</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,84; 95,06</t>
+          <t>88,74; 95,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,68; 87,04</t>
+          <t>77,64; 87,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,7; 88,55</t>
+          <t>79,85; 88,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80,43; 95,35</t>
+          <t>80,89; 95,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69,14; 74,26</t>
+          <t>69,17; 74,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,95; 65,99</t>
+          <t>60,13; 65,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,67; 70,49</t>
+          <t>64,56; 70,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,49; 75,05</t>
+          <t>69,25; 74,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,59; 77,98</t>
+          <t>73,61; 77,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,22; 69,46</t>
+          <t>64,25; 69,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68,52; 73,79</t>
+          <t>68,49; 73,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73,57; 79,09</t>
+          <t>73,81; 79,14</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,08; 82,76</t>
+          <t>80,1; 82,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72,4; 75,55</t>
+          <t>72,5; 75,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,37; 78,31</t>
+          <t>75,24; 78,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,34; 82,62</t>
+          <t>74,44; 84,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,57; 77,55</t>
+          <t>74,4; 77,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,94; 69,1</t>
+          <t>65,79; 69,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,88; 73,08</t>
+          <t>69,89; 73,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,58; 70,67</t>
+          <t>51,52; 70,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77,66; 79,63</t>
+          <t>77,65; 79,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,52; 71,77</t>
+          <t>69,6; 71,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73,09; 75,23</t>
+          <t>73,06; 75,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,25; 74,35</t>
+          <t>64,25; 74,45</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>365244; 399471</t>
+          <t>366869; 399896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>312212; 349020</t>
+          <t>313976; 351198</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>317001; 352412</t>
+          <t>317599; 353888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>360717; 400107</t>
+          <t>358394; 398318</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>235136; 262460</t>
+          <t>235973; 263742</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>233748; 264073</t>
+          <t>236288; 267211</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>260452; 290331</t>
+          <t>259792; 291809</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>303393; 335512</t>
+          <t>302981; 334831</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>611351; 656313</t>
+          <t>610927; 655099</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>559327; 607035</t>
+          <t>557631; 605411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>589411; 637597</t>
+          <t>592197; 638221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>676263; 727052</t>
+          <t>675888; 723247</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>299112; 328217</t>
+          <t>298526; 326477</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>290248; 328699</t>
+          <t>290525; 329467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>258472; 294241</t>
+          <t>260420; 295661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>321773; 359366</t>
+          <t>322192; 359561</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>288907; 318294</t>
+          <t>287863; 318413</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>224590; 259780</t>
+          <t>226004; 259631</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>280322; 312063</t>
+          <t>279805; 312012</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>257875; 286340</t>
+          <t>254734; 284951</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>596758; 638612</t>
+          <t>598037; 638854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>527652; 578230</t>
+          <t>526726; 580259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>550029; 599206</t>
+          <t>550032; 596506</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>591637; 638815</t>
+          <t>593928; 637866</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>412981; 450876</t>
+          <t>414581; 451985</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>432849; 481419</t>
+          <t>433296; 481742</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>369732; 409516</t>
+          <t>369398; 409776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>435759; 607444</t>
+          <t>434480; 607491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>109586; 132808</t>
+          <t>109831; 132798</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>167320; 196652</t>
+          <t>166008; 195972</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>110787; 133752</t>
+          <t>109094; 133934</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>104018; 121981</t>
+          <t>104454; 122281</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>532678; 576311</t>
+          <t>531478; 576051</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>613307; 668149</t>
+          <t>609592; 664367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>491637; 535706</t>
+          <t>487976; 536024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>548314; 741776</t>
+          <t>553894; 743127</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>914718; 972783</t>
+          <t>919638; 976414</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>806888; 867897</t>
+          <t>806803; 867625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>837262; 895842</t>
+          <t>832320; 895069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>684482; 747047</t>
+          <t>685389; 745426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>535279; 577210</t>
+          <t>534404; 576262</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>516522; 568419</t>
+          <t>517432; 568632</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>556605; 608180</t>
+          <t>556319; 611728</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>263162; 636537</t>
+          <t>243939; 640912</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1469367; 1541750</t>
+          <t>1469949; 1540631</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1342750; 1421317</t>
+          <t>1337734; 1418575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1408282; 1489447</t>
+          <t>1411496; 1491349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>816648; 1372558</t>
+          <t>823090; 1374480</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>258332; 288853</t>
+          <t>257986; 287010</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>345258; 384632</t>
+          <t>343845; 383791</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458750; 501805</t>
+          <t>458735; 500862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315302; 354173</t>
+          <t>317761; 355252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>407206; 448765</t>
+          <t>407155; 450182</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>446160; 500712</t>
+          <t>444811; 500169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>481181; 531954</t>
+          <t>480045; 530617</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>522661; 629623</t>
+          <t>524997; 626075</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>674578; 726544</t>
+          <t>672798; 726406</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>799175; 871390</t>
+          <t>799415; 870135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>952831; 1020046</t>
+          <t>955166; 1018196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>855181; 958644</t>
+          <t>857153; 960427</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>260890; 279156</t>
+          <t>260606; 279338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>206563; 231469</t>
+          <t>206474; 231846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>228862; 254258</t>
+          <t>229286; 253914</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>190053; 225316</t>
+          <t>191138; 224927</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>855980; 919279</t>
+          <t>856251; 921333</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>662027; 728714</t>
+          <t>664011; 727121</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>696249; 758903</t>
+          <t>694971; 758740</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>508851; 549547</t>
+          <t>507085; 548256</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1127063; 1194384</t>
+          <t>1127499; 1192009</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>880009; 951717</t>
+          <t>880373; 951164</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>934467; 1006207</t>
+          <t>933991; 1003677</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>712603; 766084</t>
+          <t>714866; 766525</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2581307; 2667413</t>
+          <t>2581887; 2667541</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2468423; 2576127</t>
+          <t>2471922; 2579532</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2546660; 2646136</t>
+          <t>2542455; 2646167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2433971; 2704761</t>
+          <t>2437276; 2760795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2502467; 2602549</t>
+          <t>2496776; 2596288</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2334682; 2446693</t>
+          <t>2329612; 2448885</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2457788; 2570370</t>
+          <t>2457982; 2572920</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1793159; 2456851</t>
+          <t>1791315; 2459848</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5109629; 5239330</t>
+          <t>5108938; 5242424</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4831804; 4988530</t>
+          <t>4837660; 4992731</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5040063; 5187960</t>
+          <t>5037975; 5191049</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4270088; 5019138</t>
+          <t>4337272; 5025940</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P33_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,6; 85,67</t>
+          <t>78,2; 85,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,81; 80,33</t>
+          <t>71,71; 80,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,02; 82,47</t>
+          <t>74,16; 82,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72,38; 80,44</t>
+          <t>73,16; 80,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,94; 86,0</t>
+          <t>77,03; 85,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,14; 84,98</t>
+          <t>75,05; 84,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,86; 84,08</t>
+          <t>75,24; 84,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,53; 75,74</t>
+          <t>69,41; 76,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,99; 84,7</t>
+          <t>79,15; 84,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,19; 80,54</t>
+          <t>74,51; 80,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,3; 82,23</t>
+          <t>76,06; 82,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,12; 77,17</t>
+          <t>71,91; 77,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,01; 89,69</t>
+          <t>81,96; 90,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,53; 78,85</t>
+          <t>70,17; 79,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,2; 78,57</t>
+          <t>69,09; 78,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,11; 80,47</t>
+          <t>73,4; 81,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,61; 85,84</t>
+          <t>78,21; 85,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,86; 76,81</t>
+          <t>66,29; 76,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,16; 83,81</t>
+          <t>74,78; 83,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,8; 75,84</t>
+          <t>68,45; 76,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,37; 86,92</t>
+          <t>81,14; 86,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,68; 76,77</t>
+          <t>69,95; 77,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,48; 79,68</t>
+          <t>73,31; 79,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,21; 77,55</t>
+          <t>72,56; 78,02</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,23; 84,2</t>
+          <t>76,91; 83,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,07; 76,79</t>
+          <t>69,2; 76,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,99; 78,75</t>
+          <t>70,83; 78,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65,84; 92,05</t>
+          <t>62,94; 71,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,74; 80,7</t>
+          <t>66,37; 80,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,65; 76,32</t>
+          <t>64,04; 76,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,34; 82,68</t>
+          <t>68,31; 82,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,41; 75,41</t>
+          <t>65,71; 76,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75,78; 82,13</t>
+          <t>76,13; 82,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,95; 75,14</t>
+          <t>69,09; 75,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71,52; 78,56</t>
+          <t>71,93; 78,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,38; 90,39</t>
+          <t>65,02; 72,19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,6; 80,27</t>
+          <t>75,2; 80,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,03; 75,31</t>
+          <t>69,89; 75,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,6; 78,07</t>
+          <t>72,77; 77,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,84; 75,96</t>
+          <t>71,27; 76,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,57; 81,49</t>
+          <t>75,12; 81,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,49; 74,17</t>
+          <t>67,44; 74,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,58; 74,32</t>
+          <t>67,67; 74,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,52; 67,05</t>
+          <t>63,03; 68,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,41; 80,09</t>
+          <t>76,34; 80,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,72; 73,94</t>
+          <t>69,82; 74,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,66; 75,72</t>
+          <t>71,77; 75,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,49; 70,95</t>
+          <t>68,62; 72,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,67; 83,07</t>
+          <t>74,12; 83,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,51; 75,36</t>
+          <t>67,78; 75,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,04; 80,84</t>
+          <t>74,27; 80,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,93; 78,18</t>
+          <t>70,44; 78,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,59; 79,15</t>
+          <t>71,39; 78,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,49; 65,77</t>
+          <t>58,67; 65,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,22; 72,09</t>
+          <t>65,79; 72,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,92; 77,42</t>
+          <t>62,94; 68,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,59; 79,45</t>
+          <t>73,62; 79,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,95; 68,52</t>
+          <t>63,41; 68,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,46; 75,11</t>
+          <t>70,45; 75,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,86; 76,04</t>
+          <t>67,04; 71,51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,74; 95,12</t>
+          <t>88,66; 95,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,64; 87,18</t>
+          <t>78,03; 87,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,85; 88,43</t>
+          <t>79,8; 88,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80,89; 95,19</t>
+          <t>82,08; 94,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69,17; 74,42</t>
+          <t>69,17; 74,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,13; 65,84</t>
+          <t>60,17; 65,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,56; 70,48</t>
+          <t>64,6; 70,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,25; 74,87</t>
+          <t>69,22; 74,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,61; 77,83</t>
+          <t>73,34; 77,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,25; 69,41</t>
+          <t>64,32; 69,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68,49; 73,6</t>
+          <t>68,54; 73,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73,81; 79,14</t>
+          <t>73,32; 78,68</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,1; 82,76</t>
+          <t>80,09; 82,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72,5; 75,65</t>
+          <t>72,46; 75,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,24; 78,31</t>
+          <t>75,43; 78,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,44; 84,33</t>
+          <t>73,89; 77,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,4; 77,36</t>
+          <t>74,45; 77,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,79; 69,16</t>
+          <t>65,92; 69,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,89; 73,16</t>
+          <t>69,93; 72,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,52; 70,75</t>
+          <t>67,95; 70,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77,65; 79,68</t>
+          <t>77,54; 79,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,6; 71,83</t>
+          <t>69,57; 71,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73,06; 75,28</t>
+          <t>73,13; 75,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,25; 74,45</t>
+          <t>71,22; 73,27</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>416727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>320436</t>
+          <t>351128</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>700645</t>
+          <t>767855</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>366869; 399896</t>
+          <t>365013; 401203</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>313976; 351198</t>
+          <t>313538; 352384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>317599; 353888</t>
+          <t>318221; 353016</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>358394; 398318</t>
+          <t>395115; 435907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>235973; 263742</t>
+          <t>236249; 262911</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>236288; 267211</t>
+          <t>235983; 264315</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>259792; 291809</t>
+          <t>261107; 291974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>302981; 334831</t>
+          <t>334847; 368717</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>610927; 655099</t>
+          <t>612173; 653684</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>557631; 605411</t>
+          <t>560073; 607228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>592197; 638221</t>
+          <t>590371; 637004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>675888; 723247</t>
+          <t>735240; 792280</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>343949</t>
+          <t>369277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>271370</t>
+          <t>300550</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>615320</t>
+          <t>669828</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>298526; 326477</t>
+          <t>298354; 328353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>290525; 329467</t>
+          <t>293208; 330254</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>260420; 295661</t>
+          <t>259991; 296197</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>322192; 359561</t>
+          <t>349874; 386363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>287863; 318413</t>
+          <t>290107; 318405</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>226004; 259631</t>
+          <t>224075; 258945</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>279805; 312012</t>
+          <t>278394; 312305</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>254734; 284951</t>
+          <t>284108; 316726</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>598037; 638854</t>
+          <t>596360; 637659</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>526726; 580259</t>
+          <t>528698; 582330</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>550032; 596506</t>
+          <t>548808; 597911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>593928; 637866</t>
+          <t>647006; 695688</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524027</t>
+          <t>312369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>113661</t>
+          <t>129708</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>637688</t>
+          <t>442077</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>414581; 451985</t>
+          <t>412861; 449390</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>433296; 481742</t>
+          <t>434107; 481180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>369398; 409776</t>
+          <t>368567; 408741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>434480; 607491</t>
+          <t>290829; 331637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>109831; 132798</t>
+          <t>109215; 131935</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>166008; 195972</t>
+          <t>164430; 195608</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>109094; 133934</t>
+          <t>110659; 133142</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>104454; 122281</t>
+          <t>119966; 140190</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531478; 576051</t>
+          <t>533940; 577983</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>609592; 664367</t>
+          <t>610890; 666046</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>487976; 536024</t>
+          <t>490775; 536498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>553894; 743127</t>
+          <t>419160; 465362</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>718736</t>
+          <t>802647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>495400</t>
+          <t>551358</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1214136</t>
+          <t>1354004</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>919638; 976414</t>
+          <t>914830; 974989</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>806803; 867625</t>
+          <t>805127; 869053</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>832320; 895069</t>
+          <t>834274; 893343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>685389; 745426</t>
+          <t>769052; 828849</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>534404; 576262</t>
+          <t>531252; 574808</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>517432; 568632</t>
+          <t>517053; 569753</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>556319; 611728</t>
+          <t>557005; 610076</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>243939; 640912</t>
+          <t>527315; 573848</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1469949; 1540631</t>
+          <t>1468449; 1543649</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1337734; 1418575</t>
+          <t>1339637; 1420716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1411496; 1491349</t>
+          <t>1413676; 1493385</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>823090; 1374480</t>
+          <t>1314556; 1391462</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336422</t>
+          <t>408072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>525564</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>897560</t>
+          <t>933635</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>257986; 287010</t>
+          <t>256093; 286795</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>343845; 383791</t>
+          <t>345176; 384820</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458735; 500862</t>
+          <t>460196; 500856</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>317761; 355252</t>
+          <t>385796; 429997</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>407155; 450182</t>
+          <t>406051; 449135</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>444811; 500169</t>
+          <t>446180; 499972</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>480045; 530617</t>
+          <t>484251; 533023</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>524997; 626075</t>
+          <t>502281; 546627</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>672798; 726406</t>
+          <t>673094; 725448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>799415; 870135</t>
+          <t>805203; 873023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>955166; 1018196</t>
+          <t>955022; 1020938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>857153; 960427</t>
+          <t>902074; 962283</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213114</t>
+          <t>210039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>529446</t>
+          <t>587208</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>742561</t>
+          <t>797247</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>260606; 279338</t>
+          <t>260379; 279530</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>206474; 231846</t>
+          <t>207517; 231739</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>229286; 253914</t>
+          <t>229142; 253958</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>191138; 224927</t>
+          <t>191754; 221715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>856251; 921333</t>
+          <t>856276; 920023</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>664011; 727121</t>
+          <t>664488; 727233</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>694971; 758740</t>
+          <t>695405; 759247</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>507085; 548256</t>
+          <t>563089; 609907</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1127499; 1192009</t>
+          <t>1123331; 1194058</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>880373; 951164</t>
+          <t>881381; 951480</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933991; 1003677</t>
+          <t>934739; 1004673</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>714866; 766525</t>
+          <t>767651; 823808</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2516458</t>
+          <t>2519131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2291453</t>
+          <t>2445515</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4807910</t>
+          <t>4964645</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2581887; 2667541</t>
+          <t>2581476; 2665998</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2471922; 2579532</t>
+          <t>2470748; 2577937</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2542455; 2646167</t>
+          <t>2548673; 2647719</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2437276; 2760795</t>
+          <t>2467331; 2573425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2496776; 2596288</t>
+          <t>2498629; 2595739</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2329612; 2448885</t>
+          <t>2334195; 2447148</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2457982; 2572920</t>
+          <t>2459329; 2566475</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1791315; 2459848</t>
+          <t>2397336; 2494032</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5108938; 5242424</t>
+          <t>5101839; 5237043</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4837660; 4992731</t>
+          <t>4835294; 4993194</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5037975; 5191049</t>
+          <t>5043337; 5189039</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4337272; 5025940</t>
+          <t>4890479; 5031247</t>
         </is>
       </c>
     </row>
